--- a/dl/c3eba6d559d70c704a79/Numbersmith_Cap_Table_and_Dilution_Calculator.xlsx
+++ b/dl/c3eba6d559d70c704a79/Numbersmith_Cap_Table_and_Dilution_Calculator.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="217">
   <si>
     <t xml:space="preserve">Numbersmith  |  Cap Table and Dilution Calculator</t>
   </si>
@@ -343,7 +343,7 @@
     <t xml:space="preserve">SAFE and Note Conversion</t>
   </si>
   <si>
-    <t xml:space="preserve">Cap price = Valuation Cap / Pre-Round Fully Diluted Shares above. Discount price approximates the round price as Pre-Money Valuation / Pre-Round Fully Diluted Shares, then applies the discount; each instrument converts at whichever price is lower. A post-money SAFE instead converts at Amount / Cap of ownership, solved directly for a share count.</t>
+    <t xml:space="preserve">Cap price for a pre-money SAFE or a note = Valuation Cap / Pre-Round Fully Diluted Shares. Cap price for a post-money SAFE = Valuation Cap / Company Capitalization, where Company Capitalization counts the pre-round shares plus every converting SAFE and note, including the post-money SAFEs themselves (the YC post-money SAFE definition). That is why a post-money SAFE's ownership percent (column K) holds at Amount / Cap no matter how many other instruments convert; the workbook solves this in closed form with no circular reference. Discount price approximates the round price as Pre-Money / Pre-Round Shares times (1 minus discount). Each instrument converts at the lower of its cap price and discount price; with neither, at the approximate round price. With two or more post-money SAFEs, each cap is assumed to bind.</t>
   </si>
   <si>
     <t xml:space="preserve">Type</t>
@@ -367,9 +367,18 @@
     <t xml:space="preserve">Conversion Shares</t>
   </si>
   <si>
+    <t xml:space="preserve">Post-Money SAFE Ownership % (Amount / Cap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed-Price Shares (pre-money SAFEs, notes)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total SAFE / Note Conversion Shares</t>
   </si>
   <si>
+    <t xml:space="preserve">Check: each post-money SAFE holds Amount / Cap of pre-money capitalization?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Option Pool Shuffle and Price Per Share</t>
   </si>
   <si>
@@ -478,7 +487,7 @@
     <t xml:space="preserve">Accrued Amt</t>
   </si>
   <si>
-    <t xml:space="preserve">Cap Price/Sh</t>
+    <t xml:space="preserve">Cap Price/Sh (pre-money SAFEs, notes)</t>
   </si>
   <si>
     <t xml:space="preserve">Scenario A Shares</t>
@@ -488,6 +497,18 @@
   </si>
   <si>
     <t xml:space="preserve">Scenario C Shares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed-Price Shares A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed-Price Shares B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed-Price Shares C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-money SAFE shares use the same Company Capitalization rule as Priced Round: Amount / Cap of the pre-round shares plus every converting instrument, solved in closed form from columns K to N. Fixed-price shares (pre-money SAFEs, notes, uncapped SAFEs) are computed per scenario because the discount price moves with each scenario's pre-money valuation.</t>
   </si>
   <si>
     <t xml:space="preserve">Scenario Results</t>
@@ -1262,13 +1283,13 @@
                 <c:formatCode>0.00%;\(0.00%\);\-</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.623955431754875</c:v>
+                  <c:v>0.622222222222222</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.623955431754875</c:v>
+                  <c:v>0.622222222222222</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.614572643307433</c:v>
+                  <c:v>0.612865497076023</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1363,13 +1384,13 @@
                 <c:formatCode>0.00%;\(0.00%\);\-</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.519962859795729</c:v>
+                  <c:v>0.518518518518519</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.519962859795729</c:v>
+                  <c:v>0.518518518518519</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.512143869422861</c:v>
+                  <c:v>0.510721247563353</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1377,11 +1398,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="53016942"/>
-        <c:axId val="44420664"/>
+        <c:axId val="86136868"/>
+        <c:axId val="84697887"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="53016942"/>
+        <c:axId val="86136868"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1447,7 +1468,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44420664"/>
+        <c:crossAx val="84697887"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1455,7 +1476,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44420664"/>
+        <c:axId val="84697887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1531,7 +1552,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53016942"/>
+        <c:crossAx val="86136868"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1838,7 +1859,7 @@
                 <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>12479108.6350975</c:v>
+                  <c:v>12444444.4444444</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1847,7 +1868,7 @@
                   <c:v>2000000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1520891.36490251</c:v>
+                  <c:v>1555555.55555556</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>4000000</c:v>
@@ -1951,7 +1972,7 @@
                 <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>46796657.3816156</c:v>
+                  <c:v>46666666.6666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1960,7 +1981,7 @@
                   <c:v>7500000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5703342.6183844</c:v>
+                  <c:v>5833333.33333333</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>15000000</c:v>
@@ -1971,11 +1992,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="24262150"/>
-        <c:axId val="49078007"/>
+        <c:axId val="27651601"/>
+        <c:axId val="87116779"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24262150"/>
+        <c:axId val="27651601"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2041,7 +2062,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49078007"/>
+        <c:crossAx val="87116779"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2049,7 +2070,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49078007"/>
+        <c:axId val="87116779"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2125,7 +2146,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24262150"/>
+        <c:crossAx val="27651601"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2623,9 +2644,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>135360</xdr:colOff>
+      <xdr:colOff>135000</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>169920</xdr:rowOff>
+      <xdr:rowOff>169560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2633,8 +2654,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="281880" y="10248840"/>
-        <a:ext cx="6478920" cy="3598920"/>
+        <a:off x="281880" y="10401480"/>
+        <a:ext cx="6478560" cy="3598560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2658,9 +2679,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>432360</xdr:colOff>
+      <xdr:colOff>432000</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>149040</xdr:rowOff>
+      <xdr:rowOff>148680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2669,7 +2690,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="281880" y="11649240"/>
-        <a:ext cx="7198920" cy="3958920"/>
+        <a:ext cx="7198560" cy="3958560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3721,7 +3742,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -3731,6 +3752,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3903,8 +3926,10 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-    </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>104</v>
       </c>
@@ -3917,6 +3942,8 @@
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
@@ -3949,6 +3976,12 @@
       <c r="J22" s="15" t="s">
         <v>111</v>
       </c>
+      <c r="K22" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="n">
@@ -3974,21 +4007,29 @@
         <f aca="false">'SAFEs and Notes'!F5</f>
         <v>0</v>
       </c>
-      <c r="G23" s="34" t="str">
-        <f aca="false">IF(AND(E23&gt;0,C23&lt;&gt;"Post-money SAFE"),E23/$D$16,"")</f>
+      <c r="G23" s="34" t="n">
+        <f aca="false">IF(E23=0,"",IF(C23="Post-money SAFE",E23*(1-$K$29)/($D$16+$L$29),E23/$D$16))</f>
+        <v>0.8</v>
+      </c>
+      <c r="H23" s="34" t="str">
+        <f aca="false">IF(F23&gt;0,($D$5/$D$16)*(1-F23),"")</f>
         <v/>
       </c>
-      <c r="H23" s="34" t="str">
-        <f aca="false">IF(AND(F23&gt;0,C23&lt;&gt;"Post-money SAFE"),($D$5/$D$16)*(1-F23),"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="34" t="str">
-        <f aca="false">IF(D23=0,"",IF(C23="Post-money SAFE","",IF(AND(G23&lt;&gt;"",H23&lt;&gt;""),MIN(G23,H23),IF(G23&lt;&gt;"",G23,IF(H23&lt;&gt;"",H23,"")))))</f>
-        <v/>
+      <c r="I23" s="34" t="n">
+        <f aca="false">IF(D23=0,"",IF(AND(G23&lt;&gt;"",H23&lt;&gt;""),MIN(G23,H23),IF(G23&lt;&gt;"",G23,IF(H23&lt;&gt;"",H23,$D$5/$D$16))))</f>
+        <v>0.8</v>
       </c>
       <c r="J23" s="35" t="n">
-        <f aca="false">IF(D23=0,0,IF(C23="Post-money SAFE",(D23/E23)*$D$16/(1-(D23/E23)),IF(I23="",0,D23/I23)))</f>
-        <v>600000</v>
+        <f aca="false">IF(D23=0,0,IF(I23="",0,D23/I23))</f>
+        <v>625000</v>
+      </c>
+      <c r="K23" s="18" t="n">
+        <f aca="false">IF(AND(C23="Post-money SAFE",D23&gt;0,E23&gt;0),D23/E23,0)</f>
+        <v>0.0625</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <f aca="false">IF(OR(D23=0,AND(C23="Post-money SAFE",E23&gt;0)),0,D23/IF(AND(E23&gt;0,F23&gt;0),MIN(E23/$D$16,($D$5/$D$16)*(1-F23)),IF(E23&gt;0,E23/$D$16,IF(F23&gt;0,($D$5/$D$16)*(1-F23),($D$5/$D$16)))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4016,19 +4057,27 @@
         <v>0.2</v>
       </c>
       <c r="G24" s="34" t="n">
-        <f aca="false">IF(AND(E24&gt;0,C24&lt;&gt;"Post-money SAFE"),E24/$D$16,"")</f>
+        <f aca="false">IF(E24=0,"",IF(C24="Post-money SAFE",E24*(1-$K$29)/($D$16+$L$29),E24/$D$16))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="H24" s="34" t="n">
-        <f aca="false">IF(AND(F24&gt;0,C24&lt;&gt;"Post-money SAFE"),($D$5/$D$16)*(1-F24),"")</f>
+        <f aca="false">IF(F24&gt;0,($D$5/$D$16)*(1-F24),"")</f>
         <v>1.06666666666667</v>
       </c>
       <c r="I24" s="34" t="n">
-        <f aca="false">IF(D24=0,"",IF(C24="Post-money SAFE","",IF(AND(G24&lt;&gt;"",H24&lt;&gt;""),MIN(G24,H24),IF(G24&lt;&gt;"",G24,IF(H24&lt;&gt;"",H24,"")))))</f>
+        <f aca="false">IF(D24=0,"",IF(AND(G24&lt;&gt;"",H24&lt;&gt;""),MIN(G24,H24),IF(G24&lt;&gt;"",G24,IF(H24&lt;&gt;"",H24,$D$5/$D$16))))</f>
         <v>0.666666666666667</v>
       </c>
       <c r="J24" s="35" t="n">
-        <f aca="false">IF(D24=0,0,IF(C24="Post-money SAFE",(D24/E24)*$D$16/(1-(D24/E24)),IF(I24="",0,D24/I24)))</f>
+        <f aca="false">IF(D24=0,0,IF(I24="",0,D24/I24))</f>
+        <v>375000</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <f aca="false">IF(AND(C24="Post-money SAFE",D24&gt;0,E24&gt;0),D24/E24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="35" t="n">
+        <f aca="false">IF(OR(D24=0,AND(C24="Post-money SAFE",E24&gt;0)),0,D24/IF(AND(E24&gt;0,F24&gt;0),MIN(E24/$D$16,($D$5/$D$16)*(1-F24)),IF(E24&gt;0,E24/$D$16,IF(F24&gt;0,($D$5/$D$16)*(1-F24),($D$5/$D$16)))))</f>
         <v>375000</v>
       </c>
     </row>
@@ -4057,19 +4106,27 @@
         <v>0</v>
       </c>
       <c r="G25" s="34" t="str">
-        <f aca="false">IF(AND(E25&gt;0,C25&lt;&gt;"Post-money SAFE"),E25/$D$16,"")</f>
+        <f aca="false">IF(E25=0,"",IF(C25="Post-money SAFE",E25*(1-$K$29)/($D$16+$L$29),E25/$D$16))</f>
         <v/>
       </c>
       <c r="H25" s="34" t="str">
-        <f aca="false">IF(AND(F25&gt;0,C25&lt;&gt;"Post-money SAFE"),($D$5/$D$16)*(1-F25),"")</f>
+        <f aca="false">IF(F25&gt;0,($D$5/$D$16)*(1-F25),"")</f>
         <v/>
       </c>
       <c r="I25" s="34" t="str">
-        <f aca="false">IF(D25=0,"",IF(C25="Post-money SAFE","",IF(AND(G25&lt;&gt;"",H25&lt;&gt;""),MIN(G25,H25),IF(G25&lt;&gt;"",G25,IF(H25&lt;&gt;"",H25,"")))))</f>
+        <f aca="false">IF(D25=0,"",IF(AND(G25&lt;&gt;"",H25&lt;&gt;""),MIN(G25,H25),IF(G25&lt;&gt;"",G25,IF(H25&lt;&gt;"",H25,$D$5/$D$16))))</f>
         <v/>
       </c>
       <c r="J25" s="35" t="n">
-        <f aca="false">IF(D25=0,0,IF(C25="Post-money SAFE",(D25/E25)*$D$16/(1-(D25/E25)),IF(I25="",0,D25/I25)))</f>
+        <f aca="false">IF(D25=0,0,IF(I25="",0,D25/I25))</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="18" t="n">
+        <f aca="false">IF(AND(C25="Post-money SAFE",D25&gt;0,E25&gt;0),D25/E25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="35" t="n">
+        <f aca="false">IF(OR(D25=0,AND(C25="Post-money SAFE",E25&gt;0)),0,D25/IF(AND(E25&gt;0,F25&gt;0),MIN(E25/$D$16,($D$5/$D$16)*(1-F25)),IF(E25&gt;0,E25/$D$16,IF(F25&gt;0,($D$5/$D$16)*(1-F25),($D$5/$D$16)))))</f>
         <v>0</v>
       </c>
     </row>
@@ -4098,19 +4155,27 @@
         <v>0</v>
       </c>
       <c r="G26" s="34" t="str">
-        <f aca="false">IF(AND(E26&gt;0,C26&lt;&gt;"Post-money SAFE"),E26/$D$16,"")</f>
+        <f aca="false">IF(E26=0,"",IF(C26="Post-money SAFE",E26*(1-$K$29)/($D$16+$L$29),E26/$D$16))</f>
         <v/>
       </c>
       <c r="H26" s="34" t="str">
-        <f aca="false">IF(AND(F26&gt;0,C26&lt;&gt;"Post-money SAFE"),($D$5/$D$16)*(1-F26),"")</f>
+        <f aca="false">IF(F26&gt;0,($D$5/$D$16)*(1-F26),"")</f>
         <v/>
       </c>
       <c r="I26" s="34" t="str">
-        <f aca="false">IF(D26=0,"",IF(C26="Post-money SAFE","",IF(AND(G26&lt;&gt;"",H26&lt;&gt;""),MIN(G26,H26),IF(G26&lt;&gt;"",G26,IF(H26&lt;&gt;"",H26,"")))))</f>
+        <f aca="false">IF(D26=0,"",IF(AND(G26&lt;&gt;"",H26&lt;&gt;""),MIN(G26,H26),IF(G26&lt;&gt;"",G26,IF(H26&lt;&gt;"",H26,$D$5/$D$16))))</f>
         <v/>
       </c>
       <c r="J26" s="35" t="n">
-        <f aca="false">IF(D26=0,0,IF(C26="Post-money SAFE",(D26/E26)*$D$16/(1-(D26/E26)),IF(I26="",0,D26/I26)))</f>
+        <f aca="false">IF(D26=0,0,IF(I26="",0,D26/I26))</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <f aca="false">IF(AND(C26="Post-money SAFE",D26&gt;0,E26&gt;0),D26/E26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="35" t="n">
+        <f aca="false">IF(OR(D26=0,AND(C26="Post-money SAFE",E26&gt;0)),0,D26/IF(AND(E26&gt;0,F26&gt;0),MIN(E26/$D$16,($D$5/$D$16)*(1-F26)),IF(E26&gt;0,E26/$D$16,IF(F26&gt;0,($D$5/$D$16)*(1-F26),($D$5/$D$16)))))</f>
         <v>0</v>
       </c>
     </row>
@@ -4139,19 +4204,27 @@
         <v>0</v>
       </c>
       <c r="G27" s="34" t="str">
-        <f aca="false">IF(AND(E27&gt;0,C27&lt;&gt;"Post-money SAFE"),E27/$D$16,"")</f>
+        <f aca="false">IF(E27=0,"",IF(C27="Post-money SAFE",E27*(1-$K$29)/($D$16+$L$29),E27/$D$16))</f>
         <v/>
       </c>
       <c r="H27" s="34" t="str">
-        <f aca="false">IF(AND(F27&gt;0,C27&lt;&gt;"Post-money SAFE"),($D$5/$D$16)*(1-F27),"")</f>
+        <f aca="false">IF(F27&gt;0,($D$5/$D$16)*(1-F27),"")</f>
         <v/>
       </c>
       <c r="I27" s="34" t="str">
-        <f aca="false">IF(D27=0,"",IF(C27="Post-money SAFE","",IF(AND(G27&lt;&gt;"",H27&lt;&gt;""),MIN(G27,H27),IF(G27&lt;&gt;"",G27,IF(H27&lt;&gt;"",H27,"")))))</f>
+        <f aca="false">IF(D27=0,"",IF(AND(G27&lt;&gt;"",H27&lt;&gt;""),MIN(G27,H27),IF(G27&lt;&gt;"",G27,IF(H27&lt;&gt;"",H27,$D$5/$D$16))))</f>
         <v/>
       </c>
       <c r="J27" s="35" t="n">
-        <f aca="false">IF(D27=0,0,IF(C27="Post-money SAFE",(D27/E27)*$D$16/(1-(D27/E27)),IF(I27="",0,D27/I27)))</f>
+        <f aca="false">IF(D27=0,0,IF(I27="",0,D27/I27))</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <f aca="false">IF(AND(C27="Post-money SAFE",D27&gt;0,E27&gt;0),D27/E27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="35" t="n">
+        <f aca="false">IF(OR(D27=0,AND(C27="Post-money SAFE",E27&gt;0)),0,D27/IF(AND(E27&gt;0,F27&gt;0),MIN(E27/$D$16,($D$5/$D$16)*(1-F27)),IF(E27&gt;0,E27/$D$16,IF(F27&gt;0,($D$5/$D$16)*(1-F27),($D$5/$D$16)))))</f>
         <v>0</v>
       </c>
     </row>
@@ -4180,26 +4253,34 @@
         <v>0</v>
       </c>
       <c r="G28" s="34" t="str">
-        <f aca="false">IF(AND(E28&gt;0,C28&lt;&gt;"Post-money SAFE"),E28/$D$16,"")</f>
+        <f aca="false">IF(E28=0,"",IF(C28="Post-money SAFE",E28*(1-$K$29)/($D$16+$L$29),E28/$D$16))</f>
         <v/>
       </c>
       <c r="H28" s="34" t="str">
-        <f aca="false">IF(AND(F28&gt;0,C28&lt;&gt;"Post-money SAFE"),($D$5/$D$16)*(1-F28),"")</f>
+        <f aca="false">IF(F28&gt;0,($D$5/$D$16)*(1-F28),"")</f>
         <v/>
       </c>
       <c r="I28" s="34" t="str">
-        <f aca="false">IF(D28=0,"",IF(C28="Post-money SAFE","",IF(AND(G28&lt;&gt;"",H28&lt;&gt;""),MIN(G28,H28),IF(G28&lt;&gt;"",G28,IF(H28&lt;&gt;"",H28,"")))))</f>
+        <f aca="false">IF(D28=0,"",IF(AND(G28&lt;&gt;"",H28&lt;&gt;""),MIN(G28,H28),IF(G28&lt;&gt;"",G28,IF(H28&lt;&gt;"",H28,$D$5/$D$16))))</f>
         <v/>
       </c>
       <c r="J28" s="35" t="n">
-        <f aca="false">IF(D28=0,0,IF(C28="Post-money SAFE",(D28/E28)*$D$16/(1-(D28/E28)),IF(I28="",0,D28/I28)))</f>
+        <f aca="false">IF(D28=0,0,IF(I28="",0,D28/I28))</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="18" t="n">
+        <f aca="false">IF(AND(C28="Post-money SAFE",D28&gt;0,E28&gt;0),D28/E28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="35" t="n">
+        <f aca="false">IF(OR(D28=0,AND(C28="Post-money SAFE",E28&gt;0)),0,D28/IF(AND(E28&gt;0,F28&gt;0),MIN(E28/$D$16,($D$5/$D$16)*(1-F28)),IF(E28&gt;0,E28/$D$16,IF(F28&gt;0,($D$5/$D$16)*(1-F28),($D$5/$D$16)))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="19"/>
       <c r="B29" s="20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -4210,12 +4291,29 @@
       <c r="I29" s="19"/>
       <c r="J29" s="36" t="n">
         <f aca="false">SUM(J23:J28)</f>
-        <v>975000</v>
+        <v>1000000</v>
+      </c>
+      <c r="K29" s="22" t="n">
+        <f aca="false">SUM(K23:K28)</f>
+        <v>0.0625</v>
+      </c>
+      <c r="L29" s="36" t="n">
+        <f aca="false">SUM(L23:L28)</f>
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="23" t="str">
+        <f aca="false">IF($K$29&gt;=1,"ERROR",IF(ROUND(SUMPRODUCT(($C$23:$C$28="Post-money SAFE")*($E$23:$E$28&gt;0)*$J$23:$J$28)/($D$16+$J$29)-$K$29,6)=0,"OK","ERROR"))</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -4229,7 +4327,7 @@
     </row>
     <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -4243,7 +4341,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="23" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D33" s="28" t="n">
         <f aca="false">D5+D13</f>
@@ -4252,7 +4350,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="23" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D34" s="37" t="n">
         <f aca="false">D6*(D33/D5)</f>
@@ -4261,52 +4359,52 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="23" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D35" s="35" t="n">
         <f aca="false">D16+J29</f>
-        <v>9975000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D36" s="35" t="n">
         <f aca="false">MAX((D34*D35-D17)/(1-IF(D7="Yes",D34,D6)),0)</f>
-        <v>282142.857142857</v>
+        <v>285714.285714286</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D37" s="38" t="n">
         <f aca="false">IF(D7="Yes",D5/(D35+D36),D5/D35)</f>
-        <v>1.16991643454039</v>
+        <v>1.16666666666667</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D38" s="35" t="n">
         <f aca="false">D13/D37</f>
-        <v>2564285.71428571</v>
+        <v>2571428.57142857</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D39" s="39" t="n">
         <f aca="false">D35+D36+D38</f>
-        <v>12821428.5714286</v>
+        <v>12857142.8571429</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="23" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D40" s="28" t="n">
         <f aca="false">D37*D39</f>
@@ -4315,7 +4413,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="23" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D41" s="23" t="str">
         <f aca="false">IF(ROUND(D40-D33,2)=0,"OK","ERROR")</f>
@@ -4324,7 +4422,7 @@
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -4350,7 +4448,7 @@
         <v>57</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4371,7 +4469,7 @@
       </c>
       <c r="E45" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D45/$D$39)</f>
-        <v>0.350974930362117</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4392,7 +4490,7 @@
       </c>
       <c r="E46" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D46/$D$39)</f>
-        <v>0.272980501392758</v>
+        <v>0.272222222222222</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4413,7 +4511,7 @@
       </c>
       <c r="E47" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D47/$D$39)</f>
-        <v>0.0779944289693593</v>
+        <v>0.0777777777777778</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4607,18 +4705,18 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C57" s="23" t="s">
         <v>65</v>
       </c>
       <c r="D57" s="35" t="n">
         <f aca="false">D36</f>
-        <v>282142.857142857</v>
+        <v>285714.285714286</v>
       </c>
       <c r="E57" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D57/$D$39)</f>
-        <v>0.0220055710306407</v>
+        <v>0.0222222222222222</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4632,11 +4730,11 @@
       </c>
       <c r="D58" s="35" t="n">
         <f aca="false">J23</f>
-        <v>600000</v>
+        <v>625000</v>
       </c>
       <c r="E58" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D58/$D$39)</f>
-        <v>0.0467966573816156</v>
+        <v>0.0486111111111111</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4654,7 +4752,7 @@
       </c>
       <c r="E59" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D59/$D$39)</f>
-        <v>0.0292479108635098</v>
+        <v>0.0291666666666667</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4740,7 +4838,7 @@
       </c>
       <c r="D64" s="35" t="n">
         <f aca="false">D10/$D$37</f>
-        <v>2564285.71428571</v>
+        <v>2571428.57142857</v>
       </c>
       <c r="E64" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D64/$D$39)</f>
@@ -4791,7 +4889,7 @@
       <c r="C67" s="19"/>
       <c r="D67" s="36" t="n">
         <f aca="false">SUM(D45:D66)</f>
-        <v>12821428.5714286</v>
+        <v>12857142.8571429</v>
       </c>
       <c r="E67" s="22" t="n">
         <f aca="false">SUM(E45:E66)</f>
@@ -4800,7 +4898,7 @@
     </row>
     <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -4822,7 +4920,7 @@
         <v>57</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4835,12 +4933,12 @@
       </c>
       <c r="E71" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D71/$D$39)</f>
-        <v>0.623955431754875</v>
+        <v>0.622222222222222</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="23" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D72" s="35" t="n">
         <f aca="false">SUMIF($C$45:$C$66,"Employee",$D$45:$D$66)</f>
@@ -4853,7 +4951,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="23" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D73" s="35" t="n">
         <f aca="false">SUMIF($C$45:$C$66,"Advisor",$D$45:$D$66)</f>
@@ -4870,7 +4968,7 @@
       </c>
       <c r="D74" s="35" t="n">
         <f aca="false">SUMIF($C$45:$C$66,"Option Pool",$D$45:$D$66)</f>
-        <v>1282142.85714286</v>
+        <v>1285714.28571429</v>
       </c>
       <c r="E74" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D74/$D$39)</f>
@@ -4879,24 +4977,24 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="23" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D75" s="35" t="n">
         <f aca="false">SUMIF($C$45:$C$66,"Converted SAFE/Note",$D$45:$D$66)</f>
-        <v>975000</v>
+        <v>1000000</v>
       </c>
       <c r="E75" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D75/$D$39)</f>
-        <v>0.0760445682451254</v>
+        <v>0.0777777777777778</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="23" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D76" s="35" t="n">
         <f aca="false">SUMIF($C$45:$C$66,"New Investor",$D$45:$D$66)</f>
-        <v>2564285.71428571</v>
+        <v>2571428.57142857</v>
       </c>
       <c r="E76" s="18" t="n">
         <f aca="false">IF($D$39=0,0,D76/$D$39)</f>
@@ -4910,7 +5008,7 @@
       <c r="C77" s="19"/>
       <c r="D77" s="36" t="n">
         <f aca="false">SUM(D71:D76)</f>
-        <v>12821428.5714286</v>
+        <v>12857142.8571429</v>
       </c>
       <c r="E77" s="22" t="n">
         <f aca="false">SUM(E71:E76)</f>
@@ -4923,8 +5021,8 @@
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A21:L21"/>
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A43:J43"/>
@@ -4951,13 +5049,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="11" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4976,7 +5075,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4990,7 +5089,7 @@
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -5000,27 +5099,27 @@
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="23"/>
       <c r="C5" s="40" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="23" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5039,7 +5138,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C8" s="25" t="n">
         <v>2500000</v>
@@ -5067,7 +5166,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="23" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>91</v>
@@ -5081,7 +5180,7 @@
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -5090,7 +5189,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="23" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C13" s="30" t="n">
         <f aca="false">'Current Cap Table'!$D$18</f>
@@ -5099,7 +5198,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C14" s="34" t="n">
         <f aca="false">C7/$C$13</f>
@@ -5116,7 +5215,7 @@
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -5127,6 +5226,10 @@
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
@@ -5145,19 +5248,31 @@
         <v>77</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>152</v>
+        <v>155</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5184,21 +5299,37 @@
         <f aca="false">'SAFEs and Notes'!I5</f>
         <v>500000</v>
       </c>
-      <c r="G18" s="34" t="n">
-        <f aca="false">IF(D18&gt;0,D18/$C$13,"")</f>
-        <v>0.888888888888889</v>
+      <c r="G18" s="34" t="str">
+        <f aca="false">IF(OR(D18=0,C18="Post-money SAFE"),"",D18/$C$13)</f>
+        <v/>
       </c>
       <c r="H18" s="35" t="n">
-        <f aca="false">IF(F18=0,0,IF(C18="Post-money SAFE",(F18/D18)*$C$13/(1-(F18/D18)),IF(AND(G18&lt;&gt;"",E18&gt;0),F18/MIN(G18,$C$14*(1-E18)),IF(G18&lt;&gt;"",F18/G18,IF(E18&gt;0,F18/($C$14*(1-E18)),0)))))</f>
-        <v>600000</v>
+        <f aca="false">IF(F18=0,0,IF(AND(C18="Post-money SAFE",D18&gt;0),MAX($K18*($C$13+L$24)/(1-$K$24),IF(E18&gt;0,F18/($C$14*(1-E18)),0)),L18))</f>
+        <v>625000</v>
       </c>
       <c r="I18" s="35" t="n">
-        <f aca="false">IF(F18=0,0,IF(C18="Post-money SAFE",(F18/D18)*$C$13/(1-(F18/D18)),IF(AND(G18&lt;&gt;"",E18&gt;0),F18/MIN(G18,$D$14*(1-E18)),IF(G18&lt;&gt;"",F18/G18,IF(E18&gt;0,F18/($D$14*(1-E18)),0)))))</f>
-        <v>600000</v>
+        <f aca="false">IF(F18=0,0,IF(AND(C18="Post-money SAFE",D18&gt;0),MAX($K18*($C$13+M$24)/(1-$K$24),IF(E18&gt;0,F18/($D$14*(1-E18)),0)),M18))</f>
+        <v>625000</v>
       </c>
       <c r="J18" s="35" t="n">
-        <f aca="false">IF(F18=0,0,IF(C18="Post-money SAFE",(F18/D18)*$C$13/(1-(F18/D18)),IF(AND(G18&lt;&gt;"",E18&gt;0),F18/MIN(G18,$E$14*(1-E18)),IF(G18&lt;&gt;"",F18/G18,IF(E18&gt;0,F18/($E$14*(1-E18)),0)))))</f>
-        <v>600000</v>
+        <f aca="false">IF(F18=0,0,IF(AND(C18="Post-money SAFE",D18&gt;0),MAX($K18*($C$13+N$24)/(1-$K$24),IF(E18&gt;0,F18/($E$14*(1-E18)),0)),N18))</f>
+        <v>625000</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <f aca="false">IF(AND(C18="Post-money SAFE",F18&gt;0,D18&gt;0),F18/D18,0)</f>
+        <v>0.0625</v>
+      </c>
+      <c r="L18" s="35" t="n">
+        <f aca="false">IF(OR(F18=0,AND(C18="Post-money SAFE",D18&gt;0)),0,F18/IF(AND(D18&gt;0,E18&gt;0),MIN(D18/$C$13,$C$14*(1-E18)),IF(D18&gt;0,D18/$C$13,IF(E18&gt;0,$C$14*(1-E18),$C$14))))</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="35" t="n">
+        <f aca="false">IF(OR(F18=0,AND(C18="Post-money SAFE",D18&gt;0)),0,F18/IF(AND(D18&gt;0,E18&gt;0),MIN(D18/$C$13,$D$14*(1-E18)),IF(D18&gt;0,D18/$C$13,IF(E18&gt;0,$D$14*(1-E18),$D$14))))</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="35" t="n">
+        <f aca="false">IF(OR(F18=0,AND(C18="Post-money SAFE",D18&gt;0)),0,F18/IF(AND(D18&gt;0,E18&gt;0),MIN(D18/$C$13,$E$14*(1-E18)),IF(D18&gt;0,D18/$C$13,IF(E18&gt;0,$E$14*(1-E18),$E$14))))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5226,19 +5357,35 @@
         <v>250000</v>
       </c>
       <c r="G19" s="34" t="n">
-        <f aca="false">IF(D19&gt;0,D19/$C$13,"")</f>
+        <f aca="false">IF(OR(D19=0,C19="Post-money SAFE"),"",D19/$C$13)</f>
         <v>0.666666666666667</v>
       </c>
       <c r="H19" s="35" t="n">
-        <f aca="false">IF(F19=0,0,IF(C19="Post-money SAFE",(F19/D19)*$C$13/(1-(F19/D19)),IF(AND(G19&lt;&gt;"",E19&gt;0),F19/MIN(G19,$C$14*(1-E19)),IF(G19&lt;&gt;"",F19/G19,IF(E19&gt;0,F19/($C$14*(1-E19)),0)))))</f>
+        <f aca="false">IF(F19=0,0,IF(AND(C19="Post-money SAFE",D19&gt;0),MAX($K19*($C$13+L$24)/(1-$K$24),IF(E19&gt;0,F19/($C$14*(1-E19)),0)),L19))</f>
         <v>375000</v>
       </c>
       <c r="I19" s="35" t="n">
-        <f aca="false">IF(F19=0,0,IF(C19="Post-money SAFE",(F19/D19)*$C$13/(1-(F19/D19)),IF(AND(G19&lt;&gt;"",E19&gt;0),F19/MIN(G19,$D$14*(1-E19)),IF(G19&lt;&gt;"",F19/G19,IF(E19&gt;0,F19/($D$14*(1-E19)),0)))))</f>
+        <f aca="false">IF(F19=0,0,IF(AND(C19="Post-money SAFE",D19&gt;0),MAX($K19*($C$13+M$24)/(1-$K$24),IF(E19&gt;0,F19/($D$14*(1-E19)),0)),M19))</f>
         <v>375000</v>
       </c>
       <c r="J19" s="35" t="n">
-        <f aca="false">IF(F19=0,0,IF(C19="Post-money SAFE",(F19/D19)*$C$13/(1-(F19/D19)),IF(AND(G19&lt;&gt;"",E19&gt;0),F19/MIN(G19,$E$14*(1-E19)),IF(G19&lt;&gt;"",F19/G19,IF(E19&gt;0,F19/($E$14*(1-E19)),0)))))</f>
+        <f aca="false">IF(F19=0,0,IF(AND(C19="Post-money SAFE",D19&gt;0),MAX($K19*($C$13+N$24)/(1-$K$24),IF(E19&gt;0,F19/($E$14*(1-E19)),0)),N19))</f>
+        <v>375000</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <f aca="false">IF(AND(C19="Post-money SAFE",F19&gt;0,D19&gt;0),F19/D19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="35" t="n">
+        <f aca="false">IF(OR(F19=0,AND(C19="Post-money SAFE",D19&gt;0)),0,F19/IF(AND(D19&gt;0,E19&gt;0),MIN(D19/$C$13,$C$14*(1-E19)),IF(D19&gt;0,D19/$C$13,IF(E19&gt;0,$C$14*(1-E19),$C$14))))</f>
+        <v>375000</v>
+      </c>
+      <c r="M19" s="35" t="n">
+        <f aca="false">IF(OR(F19=0,AND(C19="Post-money SAFE",D19&gt;0)),0,F19/IF(AND(D19&gt;0,E19&gt;0),MIN(D19/$C$13,$D$14*(1-E19)),IF(D19&gt;0,D19/$C$13,IF(E19&gt;0,$D$14*(1-E19),$D$14))))</f>
+        <v>375000</v>
+      </c>
+      <c r="N19" s="35" t="n">
+        <f aca="false">IF(OR(F19=0,AND(C19="Post-money SAFE",D19&gt;0)),0,F19/IF(AND(D19&gt;0,E19&gt;0),MIN(D19/$C$13,$E$14*(1-E19)),IF(D19&gt;0,D19/$C$13,IF(E19&gt;0,$E$14*(1-E19),$E$14))))</f>
         <v>375000</v>
       </c>
     </row>
@@ -5267,19 +5414,35 @@
         <v>0</v>
       </c>
       <c r="G20" s="34" t="str">
-        <f aca="false">IF(D20&gt;0,D20/$C$13,"")</f>
+        <f aca="false">IF(OR(D20=0,C20="Post-money SAFE"),"",D20/$C$13)</f>
         <v/>
       </c>
       <c r="H20" s="35" t="n">
-        <f aca="false">IF(F20=0,0,IF(C20="Post-money SAFE",(F20/D20)*$C$13/(1-(F20/D20)),IF(AND(G20&lt;&gt;"",E20&gt;0),F20/MIN(G20,$C$14*(1-E20)),IF(G20&lt;&gt;"",F20/G20,IF(E20&gt;0,F20/($C$14*(1-E20)),0)))))</f>
+        <f aca="false">IF(F20=0,0,IF(AND(C20="Post-money SAFE",D20&gt;0),MAX($K20*($C$13+L$24)/(1-$K$24),IF(E20&gt;0,F20/($C$14*(1-E20)),0)),L20))</f>
         <v>0</v>
       </c>
       <c r="I20" s="35" t="n">
-        <f aca="false">IF(F20=0,0,IF(C20="Post-money SAFE",(F20/D20)*$C$13/(1-(F20/D20)),IF(AND(G20&lt;&gt;"",E20&gt;0),F20/MIN(G20,$D$14*(1-E20)),IF(G20&lt;&gt;"",F20/G20,IF(E20&gt;0,F20/($D$14*(1-E20)),0)))))</f>
+        <f aca="false">IF(F20=0,0,IF(AND(C20="Post-money SAFE",D20&gt;0),MAX($K20*($C$13+M$24)/(1-$K$24),IF(E20&gt;0,F20/($D$14*(1-E20)),0)),M20))</f>
         <v>0</v>
       </c>
       <c r="J20" s="35" t="n">
-        <f aca="false">IF(F20=0,0,IF(C20="Post-money SAFE",(F20/D20)*$C$13/(1-(F20/D20)),IF(AND(G20&lt;&gt;"",E20&gt;0),F20/MIN(G20,$E$14*(1-E20)),IF(G20&lt;&gt;"",F20/G20,IF(E20&gt;0,F20/($E$14*(1-E20)),0)))))</f>
+        <f aca="false">IF(F20=0,0,IF(AND(C20="Post-money SAFE",D20&gt;0),MAX($K20*($C$13+N$24)/(1-$K$24),IF(E20&gt;0,F20/($E$14*(1-E20)),0)),N20))</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <f aca="false">IF(AND(C20="Post-money SAFE",F20&gt;0,D20&gt;0),F20/D20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="35" t="n">
+        <f aca="false">IF(OR(F20=0,AND(C20="Post-money SAFE",D20&gt;0)),0,F20/IF(AND(D20&gt;0,E20&gt;0),MIN(D20/$C$13,$C$14*(1-E20)),IF(D20&gt;0,D20/$C$13,IF(E20&gt;0,$C$14*(1-E20),$C$14))))</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="35" t="n">
+        <f aca="false">IF(OR(F20=0,AND(C20="Post-money SAFE",D20&gt;0)),0,F20/IF(AND(D20&gt;0,E20&gt;0),MIN(D20/$C$13,$D$14*(1-E20)),IF(D20&gt;0,D20/$C$13,IF(E20&gt;0,$D$14*(1-E20),$D$14))))</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="35" t="n">
+        <f aca="false">IF(OR(F20=0,AND(C20="Post-money SAFE",D20&gt;0)),0,F20/IF(AND(D20&gt;0,E20&gt;0),MIN(D20/$C$13,$E$14*(1-E20)),IF(D20&gt;0,D20/$C$13,IF(E20&gt;0,$E$14*(1-E20),$E$14))))</f>
         <v>0</v>
       </c>
     </row>
@@ -5308,19 +5471,35 @@
         <v>0</v>
       </c>
       <c r="G21" s="34" t="str">
-        <f aca="false">IF(D21&gt;0,D21/$C$13,"")</f>
+        <f aca="false">IF(OR(D21=0,C21="Post-money SAFE"),"",D21/$C$13)</f>
         <v/>
       </c>
       <c r="H21" s="35" t="n">
-        <f aca="false">IF(F21=0,0,IF(C21="Post-money SAFE",(F21/D21)*$C$13/(1-(F21/D21)),IF(AND(G21&lt;&gt;"",E21&gt;0),F21/MIN(G21,$C$14*(1-E21)),IF(G21&lt;&gt;"",F21/G21,IF(E21&gt;0,F21/($C$14*(1-E21)),0)))))</f>
+        <f aca="false">IF(F21=0,0,IF(AND(C21="Post-money SAFE",D21&gt;0),MAX($K21*($C$13+L$24)/(1-$K$24),IF(E21&gt;0,F21/($C$14*(1-E21)),0)),L21))</f>
         <v>0</v>
       </c>
       <c r="I21" s="35" t="n">
-        <f aca="false">IF(F21=0,0,IF(C21="Post-money SAFE",(F21/D21)*$C$13/(1-(F21/D21)),IF(AND(G21&lt;&gt;"",E21&gt;0),F21/MIN(G21,$D$14*(1-E21)),IF(G21&lt;&gt;"",F21/G21,IF(E21&gt;0,F21/($D$14*(1-E21)),0)))))</f>
+        <f aca="false">IF(F21=0,0,IF(AND(C21="Post-money SAFE",D21&gt;0),MAX($K21*($C$13+M$24)/(1-$K$24),IF(E21&gt;0,F21/($D$14*(1-E21)),0)),M21))</f>
         <v>0</v>
       </c>
       <c r="J21" s="35" t="n">
-        <f aca="false">IF(F21=0,0,IF(C21="Post-money SAFE",(F21/D21)*$C$13/(1-(F21/D21)),IF(AND(G21&lt;&gt;"",E21&gt;0),F21/MIN(G21,$E$14*(1-E21)),IF(G21&lt;&gt;"",F21/G21,IF(E21&gt;0,F21/($E$14*(1-E21)),0)))))</f>
+        <f aca="false">IF(F21=0,0,IF(AND(C21="Post-money SAFE",D21&gt;0),MAX($K21*($C$13+N$24)/(1-$K$24),IF(E21&gt;0,F21/($E$14*(1-E21)),0)),N21))</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <f aca="false">IF(AND(C21="Post-money SAFE",F21&gt;0,D21&gt;0),F21/D21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="35" t="n">
+        <f aca="false">IF(OR(F21=0,AND(C21="Post-money SAFE",D21&gt;0)),0,F21/IF(AND(D21&gt;0,E21&gt;0),MIN(D21/$C$13,$C$14*(1-E21)),IF(D21&gt;0,D21/$C$13,IF(E21&gt;0,$C$14*(1-E21),$C$14))))</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="35" t="n">
+        <f aca="false">IF(OR(F21=0,AND(C21="Post-money SAFE",D21&gt;0)),0,F21/IF(AND(D21&gt;0,E21&gt;0),MIN(D21/$C$13,$D$14*(1-E21)),IF(D21&gt;0,D21/$C$13,IF(E21&gt;0,$D$14*(1-E21),$D$14))))</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="35" t="n">
+        <f aca="false">IF(OR(F21=0,AND(C21="Post-money SAFE",D21&gt;0)),0,F21/IF(AND(D21&gt;0,E21&gt;0),MIN(D21/$C$13,$E$14*(1-E21)),IF(D21&gt;0,D21/$C$13,IF(E21&gt;0,$E$14*(1-E21),$E$14))))</f>
         <v>0</v>
       </c>
     </row>
@@ -5349,19 +5528,35 @@
         <v>0</v>
       </c>
       <c r="G22" s="34" t="str">
-        <f aca="false">IF(D22&gt;0,D22/$C$13,"")</f>
+        <f aca="false">IF(OR(D22=0,C22="Post-money SAFE"),"",D22/$C$13)</f>
         <v/>
       </c>
       <c r="H22" s="35" t="n">
-        <f aca="false">IF(F22=0,0,IF(C22="Post-money SAFE",(F22/D22)*$C$13/(1-(F22/D22)),IF(AND(G22&lt;&gt;"",E22&gt;0),F22/MIN(G22,$C$14*(1-E22)),IF(G22&lt;&gt;"",F22/G22,IF(E22&gt;0,F22/($C$14*(1-E22)),0)))))</f>
+        <f aca="false">IF(F22=0,0,IF(AND(C22="Post-money SAFE",D22&gt;0),MAX($K22*($C$13+L$24)/(1-$K$24),IF(E22&gt;0,F22/($C$14*(1-E22)),0)),L22))</f>
         <v>0</v>
       </c>
       <c r="I22" s="35" t="n">
-        <f aca="false">IF(F22=0,0,IF(C22="Post-money SAFE",(F22/D22)*$C$13/(1-(F22/D22)),IF(AND(G22&lt;&gt;"",E22&gt;0),F22/MIN(G22,$D$14*(1-E22)),IF(G22&lt;&gt;"",F22/G22,IF(E22&gt;0,F22/($D$14*(1-E22)),0)))))</f>
+        <f aca="false">IF(F22=0,0,IF(AND(C22="Post-money SAFE",D22&gt;0),MAX($K22*($C$13+M$24)/(1-$K$24),IF(E22&gt;0,F22/($D$14*(1-E22)),0)),M22))</f>
         <v>0</v>
       </c>
       <c r="J22" s="35" t="n">
-        <f aca="false">IF(F22=0,0,IF(C22="Post-money SAFE",(F22/D22)*$C$13/(1-(F22/D22)),IF(AND(G22&lt;&gt;"",E22&gt;0),F22/MIN(G22,$E$14*(1-E22)),IF(G22&lt;&gt;"",F22/G22,IF(E22&gt;0,F22/($E$14*(1-E22)),0)))))</f>
+        <f aca="false">IF(F22=0,0,IF(AND(C22="Post-money SAFE",D22&gt;0),MAX($K22*($C$13+N$24)/(1-$K$24),IF(E22&gt;0,F22/($E$14*(1-E22)),0)),N22))</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <f aca="false">IF(AND(C22="Post-money SAFE",F22&gt;0,D22&gt;0),F22/D22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="35" t="n">
+        <f aca="false">IF(OR(F22=0,AND(C22="Post-money SAFE",D22&gt;0)),0,F22/IF(AND(D22&gt;0,E22&gt;0),MIN(D22/$C$13,$C$14*(1-E22)),IF(D22&gt;0,D22/$C$13,IF(E22&gt;0,$C$14*(1-E22),$C$14))))</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="35" t="n">
+        <f aca="false">IF(OR(F22=0,AND(C22="Post-money SAFE",D22&gt;0)),0,F22/IF(AND(D22&gt;0,E22&gt;0),MIN(D22/$C$13,$D$14*(1-E22)),IF(D22&gt;0,D22/$C$13,IF(E22&gt;0,$D$14*(1-E22),$D$14))))</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="35" t="n">
+        <f aca="false">IF(OR(F22=0,AND(C22="Post-money SAFE",D22&gt;0)),0,F22/IF(AND(D22&gt;0,E22&gt;0),MIN(D22/$C$13,$E$14*(1-E22)),IF(D22&gt;0,D22/$C$13,IF(E22&gt;0,$E$14*(1-E22),$E$14))))</f>
         <v>0</v>
       </c>
     </row>
@@ -5390,26 +5585,42 @@
         <v>0</v>
       </c>
       <c r="G23" s="34" t="str">
-        <f aca="false">IF(D23&gt;0,D23/$C$13,"")</f>
+        <f aca="false">IF(OR(D23=0,C23="Post-money SAFE"),"",D23/$C$13)</f>
         <v/>
       </c>
       <c r="H23" s="35" t="n">
-        <f aca="false">IF(F23=0,0,IF(C23="Post-money SAFE",(F23/D23)*$C$13/(1-(F23/D23)),IF(AND(G23&lt;&gt;"",E23&gt;0),F23/MIN(G23,$C$14*(1-E23)),IF(G23&lt;&gt;"",F23/G23,IF(E23&gt;0,F23/($C$14*(1-E23)),0)))))</f>
+        <f aca="false">IF(F23=0,0,IF(AND(C23="Post-money SAFE",D23&gt;0),MAX($K23*($C$13+L$24)/(1-$K$24),IF(E23&gt;0,F23/($C$14*(1-E23)),0)),L23))</f>
         <v>0</v>
       </c>
       <c r="I23" s="35" t="n">
-        <f aca="false">IF(F23=0,0,IF(C23="Post-money SAFE",(F23/D23)*$C$13/(1-(F23/D23)),IF(AND(G23&lt;&gt;"",E23&gt;0),F23/MIN(G23,$D$14*(1-E23)),IF(G23&lt;&gt;"",F23/G23,IF(E23&gt;0,F23/($D$14*(1-E23)),0)))))</f>
+        <f aca="false">IF(F23=0,0,IF(AND(C23="Post-money SAFE",D23&gt;0),MAX($K23*($C$13+M$24)/(1-$K$24),IF(E23&gt;0,F23/($D$14*(1-E23)),0)),M23))</f>
         <v>0</v>
       </c>
       <c r="J23" s="35" t="n">
-        <f aca="false">IF(F23=0,0,IF(C23="Post-money SAFE",(F23/D23)*$C$13/(1-(F23/D23)),IF(AND(G23&lt;&gt;"",E23&gt;0),F23/MIN(G23,$E$14*(1-E23)),IF(G23&lt;&gt;"",F23/G23,IF(E23&gt;0,F23/($E$14*(1-E23)),0)))))</f>
+        <f aca="false">IF(F23=0,0,IF(AND(C23="Post-money SAFE",D23&gt;0),MAX($K23*($C$13+N$24)/(1-$K$24),IF(E23&gt;0,F23/($E$14*(1-E23)),0)),N23))</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="18" t="n">
+        <f aca="false">IF(AND(C23="Post-money SAFE",F23&gt;0,D23&gt;0),F23/D23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="35" t="n">
+        <f aca="false">IF(OR(F23=0,AND(C23="Post-money SAFE",D23&gt;0)),0,F23/IF(AND(D23&gt;0,E23&gt;0),MIN(D23/$C$13,$C$14*(1-E23)),IF(D23&gt;0,D23/$C$13,IF(E23&gt;0,$C$14*(1-E23),$C$14))))</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="35" t="n">
+        <f aca="false">IF(OR(F23=0,AND(C23="Post-money SAFE",D23&gt;0)),0,F23/IF(AND(D23&gt;0,E23&gt;0),MIN(D23/$C$13,$D$14*(1-E23)),IF(D23&gt;0,D23/$C$13,IF(E23&gt;0,$D$14*(1-E23),$D$14))))</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="35" t="n">
+        <f aca="false">IF(OR(F23=0,AND(C23="Post-money SAFE",D23&gt;0)),0,F23/IF(AND(D23&gt;0,E23&gt;0),MIN(D23/$C$13,$E$14*(1-E23)),IF(D23&gt;0,D23/$C$13,IF(E23&gt;0,$E$14*(1-E23),$E$14))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="19"/>
       <c r="B24" s="20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -5418,20 +5629,54 @@
       <c r="G24" s="19"/>
       <c r="H24" s="36" t="n">
         <f aca="false">SUM(H18:H23)</f>
-        <v>975000</v>
+        <v>1000000</v>
       </c>
       <c r="I24" s="36" t="n">
         <f aca="false">SUM(I18:I23)</f>
-        <v>975000</v>
+        <v>1000000</v>
       </c>
       <c r="J24" s="36" t="n">
         <f aca="false">SUM(J18:J23)</f>
-        <v>975000</v>
-      </c>
+        <v>1000000</v>
+      </c>
+      <c r="K24" s="22" t="n">
+        <f aca="false">SUM(K18:K23)</f>
+        <v>0.0625</v>
+      </c>
+      <c r="L24" s="36" t="n">
+        <f aca="false">SUM(L18:L23)</f>
+        <v>375000</v>
+      </c>
+      <c r="M24" s="36" t="n">
+        <f aca="false">SUM(M18:M23)</f>
+        <v>375000</v>
+      </c>
+      <c r="N24" s="36" t="n">
+        <f aca="false">SUM(N18:N23)</f>
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -5455,7 +5700,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="23" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C28" s="28" t="n">
         <f aca="false">C7+C8</f>
@@ -5472,7 +5717,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="23" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C29" s="37" t="n">
         <f aca="false">C9*(C28/C7)</f>
@@ -5489,75 +5734,75 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="23" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C30" s="35" t="n">
         <f aca="false">$C$13+H24</f>
-        <v>9975000</v>
+        <v>10000000</v>
       </c>
       <c r="D30" s="35" t="n">
         <f aca="false">$C$13+I24</f>
-        <v>9975000</v>
+        <v>10000000</v>
       </c>
       <c r="E30" s="35" t="n">
         <f aca="false">$C$13+J24</f>
-        <v>9975000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="23" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C31" s="35" t="n">
         <f aca="false">MAX((C29*C30-'Current Cap Table'!$D$20)/(1-IF(C10="Yes",C29,C9)),0)</f>
-        <v>282142.857142857</v>
+        <v>285714.285714286</v>
       </c>
       <c r="D31" s="35" t="n">
         <f aca="false">MAX((D29*D30-'Current Cap Table'!$D$20)/(1-IF(D10="Yes",D29,D9)),0)</f>
-        <v>282142.857142857</v>
+        <v>285714.285714286</v>
       </c>
       <c r="E31" s="35" t="n">
         <f aca="false">MAX((E29*E30-'Current Cap Table'!$D$20)/(1-IF(E10="Yes",E29,E9)),0)</f>
-        <v>301717.557251908</v>
+        <v>305343.511450382</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="23" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C32" s="34" t="n">
         <f aca="false">IF(C10="Yes",C7/(C30+C31),C7/C30)</f>
-        <v>0.974930362116992</v>
+        <v>0.972222222222222</v>
       </c>
       <c r="D32" s="34" t="n">
         <f aca="false">IF(D10="Yes",D7/(D30+D31),D7/D30)</f>
-        <v>1.16991643454039</v>
+        <v>1.16666666666667</v>
       </c>
       <c r="E32" s="34" t="n">
         <f aca="false">IF(E10="Yes",E7/(E30+E31),E7/E30)</f>
-        <v>1.45961002785515</v>
+        <v>1.45555555555556</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C33" s="35" t="n">
         <f aca="false">C30+C31+C8/C32</f>
-        <v>12821428.5714286</v>
+        <v>12857142.8571429</v>
       </c>
       <c r="D33" s="35" t="n">
         <f aca="false">D30+D31+D8/D32</f>
-        <v>12821428.5714286</v>
+        <v>12857142.8571429</v>
       </c>
       <c r="E33" s="35" t="n">
         <f aca="false">E30+E31+E8/E32</f>
-        <v>13017175.5725191</v>
+        <v>13053435.1145038</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="23" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C34" s="30" t="n">
         <f aca="false">'Current Cap Table'!$D$22</f>
@@ -5574,24 +5819,24 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="20" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C35" s="22" t="n">
         <f aca="false">C34/C33</f>
-        <v>0.623955431754875</v>
+        <v>0.622222222222222</v>
       </c>
       <c r="D35" s="22" t="n">
         <f aca="false">D34/D33</f>
-        <v>0.623955431754875</v>
+        <v>0.622222222222222</v>
       </c>
       <c r="E35" s="22" t="n">
         <f aca="false">E34/E33</f>
-        <v>0.614572643307433</v>
+        <v>0.612865497076023</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -5600,7 +5845,7 @@
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -5609,7 +5854,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="23" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D39" s="25" t="n">
         <v>40000000</v>
@@ -5617,7 +5862,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="23" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D40" s="25" t="n">
         <v>8000000</v>
@@ -5625,7 +5870,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="23" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D41" s="18" t="n">
         <f aca="false">D40/(D39+D40)</f>
@@ -5634,24 +5879,24 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="20" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C42" s="22" t="n">
         <f aca="false">C35*(1-$D$41)</f>
-        <v>0.519962859795729</v>
+        <v>0.518518518518519</v>
       </c>
       <c r="D42" s="22" t="n">
         <f aca="false">D35*(1-$D$41)</f>
-        <v>0.519962859795729</v>
+        <v>0.518518518518519</v>
       </c>
       <c r="E42" s="22" t="n">
         <f aca="false">E35*(1-$D$41)</f>
-        <v>0.512143869422861</v>
+        <v>0.510721247563353</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -5659,13 +5904,13 @@
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5675,11 +5920,11 @@
       </c>
       <c r="B46" s="18" t="n">
         <f aca="false">C35</f>
-        <v>0.623955431754875</v>
+        <v>0.622222222222222</v>
       </c>
       <c r="C46" s="18" t="n">
         <f aca="false">C42</f>
-        <v>0.519962859795729</v>
+        <v>0.518518518518519</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5689,11 +5934,11 @@
       </c>
       <c r="B47" s="18" t="n">
         <f aca="false">D35</f>
-        <v>0.623955431754875</v>
+        <v>0.622222222222222</v>
       </c>
       <c r="C47" s="18" t="n">
         <f aca="false">D42</f>
-        <v>0.519962859795729</v>
+        <v>0.518518518518519</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5703,20 +5948,21 @@
       </c>
       <c r="B48" s="18" t="n">
         <f aca="false">E35</f>
-        <v>0.614572643307433</v>
+        <v>0.612865497076023</v>
       </c>
       <c r="C48" s="18" t="n">
         <f aca="false">E42</f>
-        <v>0.512143869422861</v>
+        <v>0.510721247563353</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="A25:N25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A38:E38"/>
@@ -5763,7 +6009,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5772,7 +6018,7 @@
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -5780,7 +6026,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="23" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>20000000</v>
@@ -5788,7 +6034,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="23" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D6" s="41" t="n">
         <v>1</v>
@@ -5796,15 +6042,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="23" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -5812,7 +6058,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="23" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D10" s="32" t="n">
         <f aca="false">'Priced Round'!$D$13</f>
@@ -5821,25 +6067,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="23" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D11" s="42" t="n">
         <f aca="false">'Priced Round'!$D$38</f>
-        <v>2564285.71428571</v>
+        <v>2571428.57142857</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D12" s="42" t="n">
         <f aca="false">'Priced Round'!$D$39</f>
-        <v>12821428.5714286</v>
+        <v>12857142.8571429</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="23" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D13" s="30" t="n">
         <f aca="false">'Current Cap Table'!$D$22</f>
@@ -5848,7 +6094,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="23" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D14" s="24" t="n">
         <f aca="false">'Current Cap Table'!$D$21-'Current Cap Table'!$D$22</f>
@@ -5857,25 +6103,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="23" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D15" s="35" t="n">
         <f aca="false">'Current Cap Table'!$D$20+'Priced Round'!$D$36</f>
-        <v>1282142.85714286</v>
+        <v>1285714.28571429</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="23" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D16" s="42" t="n">
         <f aca="false">'Priced Round'!$J$29</f>
-        <v>975000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -5883,7 +6129,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="23" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D19" s="28" t="n">
         <f aca="false">D10*D6</f>
@@ -5892,7 +6138,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="23" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D20" s="28" t="n">
         <f aca="false">D5*(D11/D12)</f>
@@ -5901,7 +6147,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="23" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D21" s="23" t="str">
         <f aca="false">IF(D7="Yes","Participates (preference + pro rata)",IF(D20&gt;D19,"Converts to common","Takes preference"))</f>
@@ -5910,7 +6156,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="13" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D22" s="43" t="n">
         <f aca="false">IF(D7="Yes",MIN(D19,D5)+(D5-MIN(D19,D5))*(D11/D12),IF(D20&gt;D19,D5*(D11/D12),MIN(D19,D5)))</f>
@@ -5919,7 +6165,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="23" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D23" s="28" t="n">
         <f aca="false">D5-D22</f>
@@ -5928,25 +6174,25 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="23" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D24" s="34" t="n">
         <f aca="false">IF((D12-D11)=0,0,D23/(D12-D11))</f>
-        <v>1.55988857938719</v>
+        <v>1.55555555555556</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="23" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D25" s="34" t="n">
         <f aca="false">IF(D11=0,0,D22/D11)</f>
-        <v>1.55988857938719</v>
+        <v>1.55555555555556</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -5955,21 +6201,21 @@
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="15" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>57</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="23" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C29" s="35" t="n">
         <f aca="false">D13</f>
@@ -5977,16 +6223,16 @@
       </c>
       <c r="D29" s="28" t="n">
         <f aca="false">C29*$D$24</f>
-        <v>12479108.6350975</v>
+        <v>12444444.4444444</v>
       </c>
       <c r="E29" s="34" t="n">
         <f aca="false">$D$24</f>
-        <v>1.55988857938719</v>
+        <v>1.55555555555556</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="23" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C30" s="35" t="n">
         <f aca="false">D14</f>
@@ -5998,16 +6244,16 @@
       </c>
       <c r="E30" s="34" t="n">
         <f aca="false">$D$24</f>
-        <v>1.55988857938719</v>
+        <v>1.55555555555556</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="23" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C31" s="35" t="n">
         <f aca="false">D15</f>
-        <v>1282142.85714286</v>
+        <v>1285714.28571429</v>
       </c>
       <c r="D31" s="28" t="n">
         <f aca="false">C31*$D$24</f>
@@ -6015,33 +6261,33 @@
       </c>
       <c r="E31" s="34" t="n">
         <f aca="false">$D$24</f>
-        <v>1.55988857938719</v>
+        <v>1.55555555555556</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="23" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C32" s="35" t="n">
         <f aca="false">D16</f>
-        <v>975000</v>
+        <v>1000000</v>
       </c>
       <c r="D32" s="28" t="n">
         <f aca="false">C32*$D$24</f>
-        <v>1520891.36490251</v>
+        <v>1555555.55555556</v>
       </c>
       <c r="E32" s="34" t="n">
         <f aca="false">$D$24</f>
-        <v>1.55988857938719</v>
+        <v>1.55555555555556</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="23" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C33" s="35" t="n">
         <f aca="false">D11</f>
-        <v>2564285.71428571</v>
+        <v>2571428.57142857</v>
       </c>
       <c r="D33" s="28" t="n">
         <f aca="false">$D$22</f>
@@ -6049,7 +6295,7 @@
       </c>
       <c r="E33" s="34" t="n">
         <f aca="false">$D$25</f>
-        <v>1.55988857938719</v>
+        <v>1.55555555555556</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6058,7 +6304,7 @@
       </c>
       <c r="C34" s="36" t="n">
         <f aca="false">SUM(C29:C33)</f>
-        <v>12821428.5714286</v>
+        <v>12857142.8571429</v>
       </c>
       <c r="D34" s="29" t="n">
         <f aca="false">SUM(D29:D33)</f>
@@ -6068,7 +6314,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="23" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D35" s="23" t="str">
         <f aca="false">IF(ROUND(D34-$D$5,2)=0,"OK","ERROR")</f>
@@ -6077,7 +6323,7 @@
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -6085,7 +6331,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="23" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D38" s="25" t="n">
         <v>2000000</v>
@@ -6093,7 +6339,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="23" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D39" s="25" t="n">
         <v>20000000</v>
@@ -6101,7 +6347,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="23" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D40" s="25" t="n">
         <v>75000000</v>
@@ -6109,7 +6355,7 @@
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -6118,21 +6364,21 @@
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="15" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="23" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C44" s="28" t="n">
         <f aca="false">IF($D$7="Yes",MIN($D$19,$D$38)+($D$38-MIN($D$19,$D$38))*($D$11/$D$12),IF($D$38*($D$11/$D$12)&gt;$D$19,$D$38*($D$11/$D$12),MIN($D$19,$D$38)))</f>
@@ -6149,7 +6395,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="23" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C45" s="34" t="n">
         <f aca="false">IF(($D$12-$D$11)=0,0,($D$38-C44)/($D$12-$D$11))</f>
@@ -6157,16 +6403,16 @@
       </c>
       <c r="D45" s="34" t="n">
         <f aca="false">IF(($D$12-$D$11)=0,0,($D$39-D44)/($D$12-$D$11))</f>
-        <v>1.55988857938719</v>
+        <v>1.55555555555556</v>
       </c>
       <c r="E45" s="34" t="n">
         <f aca="false">IF(($D$12-$D$11)=0,0,($D$40-E44)/($D$12-$D$11))</f>
-        <v>5.84958217270195</v>
+        <v>5.83333333333333</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="23" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C47" s="28" t="n">
         <f aca="false">$D$13*C45</f>
@@ -6174,16 +6420,16 @@
       </c>
       <c r="D47" s="28" t="n">
         <f aca="false">$D$13*D45</f>
-        <v>12479108.6350975</v>
+        <v>12444444.4444444</v>
       </c>
       <c r="E47" s="28" t="n">
         <f aca="false">$D$13*E45</f>
-        <v>46796657.3816156</v>
+        <v>46666666.6666667</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="23" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C48" s="28" t="n">
         <f aca="false">$D$14*C45</f>
@@ -6200,7 +6446,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="23" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C49" s="28" t="n">
         <f aca="false">$D$15*C45</f>
@@ -6217,7 +6463,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="23" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C50" s="28" t="n">
         <f aca="false">$D$16*C45</f>
@@ -6225,16 +6471,16 @@
       </c>
       <c r="D50" s="28" t="n">
         <f aca="false">$D$16*D45</f>
-        <v>1520891.36490251</v>
+        <v>1555555.55555556</v>
       </c>
       <c r="E50" s="28" t="n">
         <f aca="false">$D$16*E45</f>
-        <v>5703342.6183844</v>
+        <v>5833333.33333333</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="23" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C51" s="28" t="n">
         <f aca="false">C44</f>
@@ -6268,7 +6514,7 @@
     </row>
     <row r="54" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
